--- a/evaluate-fliter-2.xlsx
+++ b/evaluate-fliter-2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,16 +440,16 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>600026</v>
+        <v>600012</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>中远海能</t>
+          <t>皖通高速</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8.0/37</t>
+          <t>8.0/36</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -458,16 +458,16 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>600131</v>
+        <v>600063</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>国网信通</t>
+          <t>皖维高新</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>10.0/134</t>
+          <t>6.0/28</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -476,34 +476,34 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>600867</v>
+        <v>600251</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>通化东宝</t>
+          <t>冠农股份</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>6.0/58</t>
+          <t>6.0/28</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>601872</v>
+        <v>600389</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>招商轮船</t>
+          <t>江山股份</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>6.0/37</t>
+          <t>6.0/63</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -512,16 +512,16 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>601877</v>
+        <v>600482</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>正泰电器</t>
+          <t>中国动力</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>7.0/139</t>
+          <t>6.0/35</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -530,37 +530,181 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>603489</v>
+        <v>600563</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>八方股份</t>
+          <t>法拉电子</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>6.0/26</t>
+          <t>7.0/62</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>605377</v>
+        <v>600598</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>华旺科技</t>
+          <t>北大荒</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>10.0/25</t>
+          <t>9.0/21</t>
         </is>
       </c>
       <c r="D8" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>600600</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>青岛啤酒</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>6.0/17</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>600989</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>宝丰能源</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>6.0/63</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>601216</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>君正集团</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>6.0/63</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>603063</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>禾望电气</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>10.0/30</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>603489</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>八方股份</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>6.0/26</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>603856</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>东宏股份</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>6.0/37</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>605117</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>德业股份</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>10.0/68</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>605183</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>确成股份</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>6.0/22</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
         <v>5</v>
       </c>
     </row>
